--- a/task-reviews/documents/task_documents_arithmetic_section_expression_value/task_documents_arithmetic_section_expression_value.xlsx
+++ b/task-reviews/documents/task_documents_arithmetic_section_expression_value/task_documents_arithmetic_section_expression_value.xlsx
@@ -4285,7 +4285,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>You are given a receipt-style document with visible section headers and labeled totals rows. In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
+          <t>Read the named sections in this document: a receipt-style document with visible section headers and labeled totals rows. Find the named section and then answer: In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
 Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
@@ -4295,16 +4295,16 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>You are given a receipt-style document with visible section headers and labeled totals rows. In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
+          <t>Read the named sections in this document: a receipt-style document with visible section headers and labeled totals rows. Find the named section and then answer: In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
 Return a valid JSON object with key "answer".
-Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Answer: set "answer" to the computed amount formatted exactly as $0.00.
 Example JSON:
 {"answer":"$42.50"}</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 768.5, 864.0, 795.5]], "answer": "$41.41"}</t>
+          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 768.5, 864.0, 795.5]], "answer": "$39.85"}</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -4323,16 +4323,16 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>535327628841395</v>
+        <v>200119639823004</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0001.png</t>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0000.png</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0001.json</t>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0000.json</t>
         </is>
       </c>
     </row>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Look at the document in the image: a receipt-style document with visible section headers and labeled totals rows. Locate the relevant section before computing the answer: In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
+          <t>The image shows a receipt-style document with visible section headers and labeled totals rows. Find the named section and then answer: In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
 Answer field: set "answer" to the computed amount formatted exactly as $0.00.
@@ -4359,16 +4359,16 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Look at the document in the image: a receipt-style document with visible section headers and labeled totals rows. Locate the relevant section before computing the answer: In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
+          <t>The image shows a receipt-style document with visible section headers and labeled totals rows. Find the named section and then answer: In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
 Return a valid JSON object with key "answer".
-Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
 Example JSON:
 {"answer":"$42.50"}</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 768.5, 864.0, 795.5]], "answer": "$39.95"}</t>
+          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 768.5, 864.0, 795.5]], "answer": "$92.81"}</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -4387,16 +4387,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>848068357182495</v>
+        <v>240439133295176</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0014.png</t>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0010.png</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0014.json</t>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0010.json</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,71 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>You are given a receipt-style document with visible section headers and labeled totals rows. Find the named section and then answer: In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
+          <t>Use the structured document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. In the Billing Summary section, what is Subtotal minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Use the structured document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. In the Billing Summary section, what is Subtotal minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$42.50"}</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [665.0, 722.5, 766.0, 749.5]], "answer": "$188.96"}</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>[[665.0, 601.5, 784.0, 628.5], [665.0, 722.5, 766.0, 749.5]]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>492826604963131</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0001.png</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0001.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="207.75" customHeight="1">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>difference_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: a structured application form with visible section headers and labeled fields. Find the named section and then answer: In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
 Answer field: set "answer" to the computed amount formatted exactly as $0.00.
@@ -4421,63 +4485,255 @@
 {"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>You are given a receipt-style document with visible section headers and labeled totals rows. Find the named section and then answer: In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: a structured application form with visible section headers and labeled fields. Find the named section and then answer: In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
 Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$42.50"}</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[218.0, 638.5, 337.0, 665.5], [218.0, 764.5, 301.0, 791.5]], "answer": "$97.33"}</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>[[218.0, 638.5, 337.0, 665.5], [218.0, 764.5, 301.0, 791.5]]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>507348000401628</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0014.png</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0014.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="207.75" customHeight="1">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>difference_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Use the structured document in the image: a structured application form with visible section headers and labeled fields. In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
 Answer field: set "answer" to the computed amount formatted exactly as $0.00.
 Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Use the structured document in the image: a structured application form with visible section headers and labeled fields. In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
 {"answer":"$42.50"}</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 768.5, 864.0, 795.5]], "answer": "$62.27"}</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 768.5, 864.0, 795.5]]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[218.0, 638.5, 337.0, 665.5], [218.0, 764.5, 319.0, 791.5]], "answer": "$105.95"}</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>[[218.0, 638.5, 337.0, 665.5], [218.0, 764.5, 319.0, 791.5]]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>943850411785552</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="K6" t="n">
+        <v>607886527956488</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0017.png</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0017.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="207.75" customHeight="1">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>difference_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>You are given an invoice with visible named sections, labeled header fields, and summary blocks. Use the visible section headers and values to answer: In the Billing Summary section, what is Subtotal minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>You are given an invoice with visible named sections, labeled header fields, and summary blocks. Use the visible section headers and values to answer: In the Billing Summary section, what is Subtotal minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$42.50"}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [665.0, 722.5, 748.0, 749.5]], "answer": "$161.88"}</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>[[665.0, 601.5, 784.0, 628.5], [665.0, 722.5, 748.0, 749.5]]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1484849663135154</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0020.png</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0020.json</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="207.75" customHeight="1">
-      <c r="C5" s="2" t="inlineStr">
+    <row r="8" ht="207.75" customHeight="1">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>task_documents_arithmetic_section_expression_value</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>difference_two_amounts_in_section</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>The image shows an invoice with visible named sections, labeled header fields, and summary blocks. In the Billing Summary section, what is Subtotal minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Read the named sections in this document: an invoice with visible named sections, labeled header fields, and summary blocks. Locate the relevant section before computing the answer: In the Billing Summary section, what is Subtotal minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Read the named sections in this document: an invoice with visible named sections, labeled header fields, and summary blocks. Locate the relevant section before computing the answer: In the Billing Summary section, what is Subtotal minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$42.50"}</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [665.0, 722.5, 766.0, 749.5]], "answer": "$154.04"}</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>[[665.0, 601.5, 784.0, 628.5], [665.0, 722.5, 766.0, 749.5]]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1897585242970790</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0004.png</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0004.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="207.75" customHeight="1">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>difference_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Use the structured document in the image: a receipt-style document with visible section headers and labeled totals rows. Use the visible section headers and values to answer: In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence requirement: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
 Answer format: set "answer" to the computed amount formatted exactly as $0.00.
@@ -4485,63 +4741,383 @@
 {"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>The image shows an invoice with visible named sections, labeled header fields, and summary blocks. In the Billing Summary section, what is Subtotal minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Use the structured document in the image: a receipt-style document with visible section headers and labeled totals rows. Use the visible section headers and values to answer: In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$42.50"}</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 768.5, 864.0, 795.5]], "answer": "$30.11"}</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 768.5, 864.0, 795.5]]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>2131599877198389</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0018.png</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0018.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="207.75" customHeight="1">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>difference_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: a structured application form with visible section headers and labeled fields. Locate the relevant section before computing the answer: In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: a structured application form with visible section headers and labeled fields. Locate the relevant section before computing the answer: In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$42.50"}</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[218.0, 638.5, 319.0, 665.5], [218.0, 764.5, 301.0, 791.5]], "answer": "$60.42"}</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>[[218.0, 638.5, 319.0, 665.5], [218.0, 764.5, 301.0, 791.5]]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>2352788527903154</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0015.png</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0015.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="207.75" customHeight="1">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>difference_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Read the named sections in this document: a structured application form with visible section headers and labeled fields. Find the named section and then answer: In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Read the named sections in this document: a structured application form with visible section headers and labeled fields. Find the named section and then answer: In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$42.50"}</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[218.0, 638.5, 319.0, 665.5], [218.0, 764.5, 301.0, 791.5]], "answer": "$92.13"}</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>[[218.0, 638.5, 319.0, 665.5], [218.0, 764.5, 301.0, 791.5]]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>2500154937888651</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0023.png</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0023.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="207.75" customHeight="1">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>difference_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: a structured application form with visible section headers and labeled fields. In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: a structured application form with visible section headers and labeled fields. In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$42.50"}</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[218.0, 638.5, 319.0, 665.5], [218.0, 764.5, 319.0, 791.5]], "answer": "$58.73"}</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>[[218.0, 638.5, 319.0, 665.5], [218.0, 764.5, 319.0, 791.5]]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>2788906996429946</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0013.png</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0013.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="207.75" customHeight="1">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>difference_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: a receipt-style document with visible section headers and labeled totals rows. In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: a receipt-style document with visible section headers and labeled totals rows. In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
 Return a valid JSON object with key "answer".
 Answer: set "answer" to the computed amount formatted exactly as $0.00.
 Example JSON:
 {"answer":"$42.50"}</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [665.0, 722.5, 766.0, 749.5]], "answer": "$233.43"}</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>[[665.0, 601.5, 784.0, 628.5], [665.0, 722.5, 766.0, 749.5]]</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 768.5, 864.0, 795.5]], "answer": "$38.93"}</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 768.5, 864.0, 795.5]]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>1088676718696001</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0005.png</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0005.json</t>
+      <c r="K13" t="n">
+        <v>2923217756137123</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0019.png</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0019.json</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="207.75" customHeight="1">
-      <c r="C6" s="2" t="inlineStr">
+    <row r="14" ht="207.75" customHeight="1">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>task_documents_arithmetic_section_expression_value</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>difference_two_amounts_in_section</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Use the structured document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. Locate the relevant section before computing the answer: In the Billing Summary section, what is Subtotal minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Read the named sections in this document: an invoice with visible named sections, labeled header fields, and summary blocks. Read the document and answer this question: In the Billing Summary section, what is Subtotal minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Read the named sections in this document: an invoice with visible named sections, labeled header fields, and summary blocks. Read the document and answer this question: In the Billing Summary section, what is Subtotal minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$42.50"}</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [665.0, 722.5, 748.0, 749.5]], "answer": "$156.34"}</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>[[665.0, 601.5, 784.0, 628.5], [665.0, 722.5, 748.0, 749.5]]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>3625531077093234</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0024.png</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0024.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="207.75" customHeight="1">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>difference_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Read the named sections in this document: an invoice with visible named sections, labeled header fields, and summary blocks. In the Billing Summary section, what is Subtotal minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
 Answer: set "answer" to the computed amount formatted exactly as $0.00.
@@ -4549,63 +5125,255 @@
 {"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Use the structured document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. Locate the relevant section before computing the answer: In the Billing Summary section, what is Subtotal minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Read the named sections in this document: an invoice with visible named sections, labeled header fields, and summary blocks. In the Billing Summary section, what is Subtotal minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
 Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
+Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
 Example JSON:
 {"answer":"$42.50"}</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [665.0, 722.5, 748.0, 749.5]], "answer": "$306.17"}</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [665.0, 722.5, 748.0, 749.5]], "answer": "$198.06"}</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>[[665.0, 601.5, 784.0, 628.5], [665.0, 722.5, 748.0, 749.5]]</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>1162072499169872</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0009.png</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0009.json</t>
+      <c r="K15" t="n">
+        <v>3792126340203704</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0021.png</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0021.json</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="207.75" customHeight="1">
-      <c r="C7" s="2" t="inlineStr">
+    <row r="16" ht="207.75" customHeight="1">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>task_documents_arithmetic_section_expression_value</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>difference_two_amounts_in_section</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>You are given a structured application form with visible section headers and labeled fields. Read the document and answer this question: In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a structured application form with visible section headers and labeled fields. Use the visible section headers and values to answer: In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer format: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a structured application form with visible section headers and labeled fields. Use the visible section headers and values to answer: In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$42.50"}</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[218.0, 638.5, 319.0, 665.5], [218.0, 764.5, 301.0, 791.5]], "answer": "$75.98"}</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>[[218.0, 638.5, 319.0, 665.5], [218.0, 764.5, 301.0, 791.5]]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>4117490650795613</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0003.png</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0003.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="207.75" customHeight="1">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>difference_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a structured application form with visible section headers and labeled fields. Read the document and answer this question: In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a structured application form with visible section headers and labeled fields. Read the document and answer this question: In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$42.50"}</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[218.0, 638.5, 337.0, 665.5], [218.0, 764.5, 301.0, 791.5]], "answer": "$101.89"}</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>[[218.0, 638.5, 337.0, 665.5], [218.0, 764.5, 301.0, 791.5]]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>4305999922072468</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0002.png</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0002.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="207.75" customHeight="1">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>difference_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>You are given a receipt-style document with visible section headers and labeled totals rows. Find the named section and then answer: In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer format: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>You are given a receipt-style document with visible section headers and labeled totals rows. Find the named section and then answer: In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$42.50"}</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 768.5, 864.0, 795.5]], "answer": "$36.53"}</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 768.5, 864.0, 795.5]]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>4349561242251844</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0008.png</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0008.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="207.75" customHeight="1">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>difference_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: a receipt-style document with visible section headers and labeled totals rows. In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
 Answer field: set "answer" to the computed amount formatted exactly as $0.00.
@@ -4613,63 +5381,191 @@
 {"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>You are given a structured application form with visible section headers and labeled fields. Read the document and answer this question: In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: a receipt-style document with visible section headers and labeled totals rows. In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
 Return a valid JSON object with key "answer".
 Answer field: set "answer" to the computed amount formatted exactly as $0.00.
 Example JSON:
 {"answer":"$42.50"}</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[218.0, 638.5, 337.0, 665.5], [218.0, 764.5, 319.0, 791.5]], "answer": "$96.57"}</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>[[218.0, 638.5, 337.0, 665.5], [218.0, 764.5, 319.0, 791.5]]</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 768.5, 864.0, 795.5]], "answer": "$69.98"}</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 768.5, 864.0, 795.5]]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>1384542232660317</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0024.png</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0024.json</t>
+      <c r="K19" t="n">
+        <v>5219963115757491</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0016.png</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0016.json</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="207.75" customHeight="1">
-      <c r="C8" s="2" t="inlineStr">
+    <row r="20" ht="207.75" customHeight="1">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>task_documents_arithmetic_section_expression_value</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>difference_two_amounts_in_section</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Look at the document in the image: a structured application form with visible section headers and labeled fields. Use the visible section headers and values to answer: In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Read the named sections in this document: a receipt-style document with visible section headers and labeled totals rows. Find the named section and then answer: In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Read the named sections in this document: a receipt-style document with visible section headers and labeled totals rows. Find the named section and then answer: In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$42.50"}</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 768.5, 864.0, 795.5]], "answer": "$95.20"}</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 768.5, 864.0, 795.5]]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>5578709858784463</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0009.png</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0009.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="207.75" customHeight="1">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>difference_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>You are given an invoice with visible named sections, labeled header fields, and summary blocks. In the Billing Summary section, what is Subtotal minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>You are given an invoice with visible named sections, labeled header fields, and summary blocks. In the Billing Summary section, what is Subtotal minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$42.50"}</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [665.0, 722.5, 766.0, 749.5]], "answer": "$225.67"}</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>[[665.0, 601.5, 784.0, 628.5], [665.0, 722.5, 766.0, 749.5]]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>5674095311087131</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0012.png</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0012.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="207.75" customHeight="1">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>difference_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>You are given a structured application form with visible section headers and labeled fields. Use the visible section headers and values to answer: In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence requirement: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
 Answer format: set "answer" to the computed amount formatted exactly as $0.00.
@@ -4677,255 +5573,191 @@
 {"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Look at the document in the image: a structured application form with visible section headers and labeled fields. Use the visible section headers and values to answer: In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>You are given a structured application form with visible section headers and labeled fields. Use the visible section headers and values to answer: In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
 Return a valid JSON object with key "answer".
-Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Answer: set "answer" to the computed amount formatted exactly as $0.00.
 Example JSON:
 {"answer":"$42.50"}</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[218.0, 638.5, 337.0, 665.5], [218.0, 764.5, 319.0, 791.5]], "answer": "$95.34"}</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>[[218.0, 638.5, 337.0, 665.5], [218.0, 764.5, 319.0, 791.5]]</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[218.0, 638.5, 337.0, 665.5], [218.0, 764.5, 301.0, 791.5]], "answer": "$107.65"}</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>[[218.0, 638.5, 337.0, 665.5], [218.0, 764.5, 301.0, 791.5]]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K8" t="n">
-        <v>1732288553350629</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="K22" t="n">
+        <v>6945613651791068</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0022.png</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0022.json</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="207.75" customHeight="1">
-      <c r="C9" s="2" t="inlineStr">
+    <row r="23" ht="207.75" customHeight="1">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>task_documents_arithmetic_section_expression_value</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>difference_two_amounts_in_section</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: an invoice with visible named sections, labeled header fields, and summary blocks. In the Billing Summary section, what is Subtotal minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Use the structured document in the image: a structured application form with visible section headers and labeled fields. In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
+Evidence: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer: set "answer" to the computed amount formatted exactly as $0.00.
 Example JSON:
 {"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: an invoice with visible named sections, labeled header fields, and summary blocks. In the Billing Summary section, what is Subtotal minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Use the structured document in the image: a structured application form with visible section headers and labeled fields. In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
 Return a valid JSON object with key "answer".
-Answer format: set "answer" to the computed amount formatted exactly as $0.00.
+Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
 Example JSON:
 {"answer":"$42.50"}</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [665.0, 722.5, 748.0, 749.5]], "answer": "$127.52"}</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>[[665.0, 601.5, 784.0, 628.5], [665.0, 722.5, 748.0, 749.5]]</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[218.0, 638.5, 319.0, 665.5], [218.0, 764.5, 301.0, 791.5]], "answer": "$78.13"}</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>[[218.0, 638.5, 319.0, 665.5], [218.0, 764.5, 301.0, 791.5]]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K9" t="n">
-        <v>1798535243231752</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="K23" t="n">
+        <v>7022051630588782</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0006.png</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0006.json</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="207.75" customHeight="1">
-      <c r="C10" s="2" t="inlineStr">
+    <row r="24" ht="207.75" customHeight="1">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>task_documents_arithmetic_section_expression_value</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>difference_two_amounts_in_section</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: a structured application form with visible section headers and labeled fields. In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>You are given an invoice with visible named sections, labeled header fields, and summary blocks. Locate the relevant section before computing the answer: In the Billing Summary section, what is Subtotal minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
+Evidence: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer: set "answer" to the computed amount formatted exactly as $0.00.
 Example JSON:
 {"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: a structured application form with visible section headers and labeled fields. In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$42.50"}</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[218.0, 638.5, 337.0, 665.5], [218.0, 764.5, 319.0, 791.5]], "answer": "$127.07"}</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>[[218.0, 638.5, 337.0, 665.5], [218.0, 764.5, 319.0, 791.5]]</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>3109132411823250</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0002.png</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0002.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="207.75" customHeight="1">
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>difference_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Look at the document in the image: a structured application form with visible section headers and labeled fields. Use the visible section headers and values to answer: In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Look at the document in the image: a structured application form with visible section headers and labeled fields. Use the visible section headers and values to answer: In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>You are given an invoice with visible named sections, labeled header fields, and summary blocks. Locate the relevant section before computing the answer: In the Billing Summary section, what is Subtotal minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
 Return a valid JSON object with key "answer".
 Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
 Example JSON:
 {"answer":"$42.50"}</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[218.0, 638.5, 337.0, 665.5], [218.0, 764.5, 319.0, 791.5]], "answer": "$123.19"}</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>[[218.0, 638.5, 337.0, 665.5], [218.0, 764.5, 319.0, 791.5]]</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [665.0, 722.5, 766.0, 749.5]], "answer": "$243.78"}</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>[[665.0, 601.5, 784.0, 628.5], [665.0, 722.5, 766.0, 749.5]]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K11" t="n">
-        <v>4281345005048484</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0016.png</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0016.json</t>
+      <c r="K24" t="n">
+        <v>7099643802831791</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0011.png</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0011.json</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="207.75" customHeight="1">
-      <c r="C12" s="2" t="inlineStr">
+    <row r="25" ht="207.75" customHeight="1">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>task_documents_arithmetic_section_expression_value</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>difference_two_amounts_in_section</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Use the structured document in the image: a receipt-style document with visible section headers and labeled totals rows. Read the document and answer this question: In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a receipt-style document with visible section headers and labeled totals rows. In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
 Answer field: set "answer" to the computed amount formatted exactly as $0.00.
@@ -4933,878 +5765,46 @@
 {"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Use the structured document in the image: a receipt-style document with visible section headers and labeled totals rows. Read the document and answer this question: In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$42.50"}</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 768.5, 864.0, 795.5]], "answer": "$23.19"}</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 768.5, 864.0, 795.5]]</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>4414030604482790</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0021.png</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0021.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="207.75" customHeight="1">
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>difference_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a structured application form with visible section headers and labeled fields. In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer field: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a structured application form with visible section headers and labeled fields. In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$42.50"}</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[218.0, 638.5, 337.0, 665.5], [218.0, 764.5, 319.0, 791.5]], "answer": "$104.28"}</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>[[218.0, 638.5, 337.0, 665.5], [218.0, 764.5, 319.0, 791.5]]</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>4609643385743424</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0018.png</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0018.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="207.75" customHeight="1">
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>difference_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: a receipt-style document with visible section headers and labeled totals rows. Find the named section and then answer: In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: a receipt-style document with visible section headers and labeled totals rows. Find the named section and then answer: In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$42.50"}</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 768.5, 864.0, 795.5]], "answer": "$66.61"}</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 768.5, 864.0, 795.5]]</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>4926653234004979</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0007.png</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0007.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="207.75" customHeight="1">
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>difference_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a structured application form with visible section headers and labeled fields. Read the document and answer this question: In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a structured application form with visible section headers and labeled fields. Read the document and answer this question: In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$42.50"}</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[218.0, 638.5, 337.0, 665.5], [218.0, 764.5, 319.0, 791.5]], "answer": "$87.70"}</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>[[218.0, 638.5, 337.0, 665.5], [218.0, 764.5, 319.0, 791.5]]</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>4994305733537202</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0004.png</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0004.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="207.75" customHeight="1">
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>difference_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Use the structured document in the image: a receipt-style document with visible section headers and labeled totals rows. Find the named section and then answer: In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Use the structured document in the image: a receipt-style document with visible section headers and labeled totals rows. Find the named section and then answer: In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$42.50"}</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 768.5, 864.0, 795.5]], "answer": "$33.11"}</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 768.5, 864.0, 795.5]]</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>6388661796480387</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0019.png</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0019.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="207.75" customHeight="1">
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>difference_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Look at the document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. Use the visible section headers and values to answer: In the Billing Summary section, what is Subtotal minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Look at the document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. Use the visible section headers and values to answer: In the Billing Summary section, what is Subtotal minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$42.50"}</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [665.0, 722.5, 766.0, 749.5]], "answer": "$112.49"}</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>[[665.0, 601.5, 784.0, 628.5], [665.0, 722.5, 766.0, 749.5]]</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>6398854852758670</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0011.png</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0011.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="207.75" customHeight="1">
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>difference_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>You are given a receipt-style document with visible section headers and labeled totals rows. Read the document and answer this question: In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>You are given a receipt-style document with visible section headers and labeled totals rows. Read the document and answer this question: In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$42.50"}</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 768.5, 864.0, 795.5]], "answer": "$25.65"}</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 768.5, 864.0, 795.5]]</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>6616773169455612</v>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0017.png</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0017.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="207.75" customHeight="1">
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>difference_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Look at the document in the image: a structured application form with visible section headers and labeled fields. Use the visible section headers and values to answer: In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Look at the document in the image: a structured application form with visible section headers and labeled fields. Use the visible section headers and values to answer: In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$42.50"}</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[218.0, 638.5, 337.0, 665.5], [218.0, 764.5, 301.0, 791.5]], "answer": "$125.22"}</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>[[218.0, 638.5, 337.0, 665.5], [218.0, 764.5, 301.0, 791.5]]</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>6867011374772382</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0008.png</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0008.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="207.75" customHeight="1">
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>difference_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: a receipt-style document with visible section headers and labeled totals rows. Find the named section and then answer: In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: a receipt-style document with visible section headers and labeled totals rows. Find the named section and then answer: In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$42.50"}</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 768.5, 864.0, 795.5]], "answer": "$52.33"}</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 768.5, 864.0, 795.5]]</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>7262305870989595</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0003.png</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0003.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="207.75" customHeight="1">
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>difference_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: a receipt-style document with visible section headers and labeled totals rows. Locate the relevant section before computing the answer: In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: a receipt-style document with visible section headers and labeled totals rows. Locate the relevant section before computing the answer: In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$42.50"}</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 768.5, 864.0, 795.5]], "answer": "$58.32"}</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 768.5, 864.0, 795.5]]</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>7595920905575084</v>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0015.png</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0015.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="207.75" customHeight="1">
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>difference_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>You are given a structured application form with visible section headers and labeled fields. Find the named section and then answer: In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>You are given a structured application form with visible section headers and labeled fields. Find the named section and then answer: In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$42.50"}</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[218.0, 638.5, 319.0, 665.5], [218.0, 764.5, 301.0, 791.5]], "answer": "$73.73"}</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>[[218.0, 638.5, 319.0, 665.5], [218.0, 764.5, 301.0, 791.5]]</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>7672885196151156</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0010.png</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0010.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="207.75" customHeight="1">
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>difference_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: a structured application form with visible section headers and labeled fields. Locate the relevant section before computing the answer: In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer field: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: a structured application form with visible section headers and labeled fields. Locate the relevant section before computing the answer: In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$42.50"}</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[218.0, 638.5, 319.0, 665.5], [218.0, 764.5, 301.0, 791.5]], "answer": "$77.13"}</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>[[218.0, 638.5, 319.0, 665.5], [218.0, 764.5, 301.0, 791.5]]</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>7768455121012613</v>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0023.png</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0023.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="207.75" customHeight="1">
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>difference_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: a receipt-style document with visible section headers and labeled totals rows. Find the named section and then answer: In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: a receipt-style document with visible section headers and labeled totals rows. Find the named section and then answer: In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a receipt-style document with visible section headers and labeled totals rows. In the Totals section, what is Items Total minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
 Return a valid JSON object with key "answer".
 Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
 Example JSON:
 {"answer":"$42.50"}</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 768.5, 864.0, 795.5]], "answer": "$71.90"}</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 768.5, 864.0, 795.5]], "answer": "$71.54"}</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 768.5, 864.0, 795.5]]</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K24" t="n">
-        <v>7790799422031645</v>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0000.png</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0000.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="207.75" customHeight="1">
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>difference_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: a structured application form with visible section headers and labeled fields. Find the named section and then answer: In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$42.50"}</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: a structured application form with visible section headers and labeled fields. Find the named section and then answer: In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$42.50"}</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[218.0, 638.5, 319.0, 665.5], [218.0, 764.5, 319.0, 791.5]], "answer": "$44.50"}</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>[[218.0, 638.5, 319.0, 665.5], [218.0, 764.5, 319.0, 791.5]]</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
       <c r="K25" t="n">
-        <v>7936628533778214</v>
+        <v>8612572591713495</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0012.png</t>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0007.png</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0012.json</t>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0007.json</t>
         </is>
       </c>
     </row>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Read the named sections in this document: a structured application form with visible section headers and labeled fields. Locate the relevant section before computing the answer: In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
+          <t>The image shows an invoice with visible named sections, labeled header fields, and summary blocks. Read the document and answer this question: In the Billing Summary section, what is Subtotal minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence requirement: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
 Answer format: set "answer" to the computed amount formatted exactly as $0.00.
@@ -5831,21 +5831,21 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Read the named sections in this document: a structured application form with visible section headers and labeled fields. Locate the relevant section before computing the answer: In the Fees section, what is Registration Fee minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
+          <t>The image shows an invoice with visible named sections, labeled header fields, and summary blocks. Read the document and answer this question: In the Billing Summary section, what is Subtotal minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
 Return a valid JSON object with key "answer".
-Answer: set "answer" to the computed amount formatted exactly as $0.00.
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
 Example JSON:
 {"answer":"$42.50"}</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": [[218.0, 638.5, 319.0, 665.5], [218.0, 764.5, 319.0, 791.5]], "answer": "$78.89"}</t>
+          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [665.0, 722.5, 766.0, 749.5]], "answer": "$253.45"}</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>[[218.0, 638.5, 319.0, 665.5], [218.0, 764.5, 319.0, 791.5]]</t>
+          <t>[[665.0, 601.5, 784.0, 628.5], [665.0, 722.5, 766.0, 749.5]]</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -5859,16 +5859,16 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>8882566418429754</v>
+        <v>8767215500303996</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0013.png</t>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/difference_two_amounts_in_section/0005.png</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0013.json</t>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/difference_two_amounts_in_section/0005.json</t>
         </is>
       </c>
     </row>
@@ -5982,7 +5982,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Look at the document in the image: a receipt-style document with visible section headers and labeled totals rows. Find the named section and then answer: In the Totals section, what is Items Total plus Tax minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
+          <t>Use the structured document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. Locate the relevant section before computing the answer: In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
 Answer: set "answer" to the computed amount formatted exactly as $0.00.
@@ -5992,21 +5992,21 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Look at the document in the image: a receipt-style document with visible section headers and labeled totals rows. Find the named section and then answer: In the Totals section, what is Items Total plus Tax minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
+          <t>Use the structured document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. Locate the relevant section before computing the answer: In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
 Return a valid JSON object with key "answer".
-Answer: set "answer" to the computed amount formatted exactly as $0.00.
+Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
 Example JSON:
 {"answer":"$133.30"}</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5], [781.0, 768.5, 864.0, 795.5]], "answer": "$76.42"}</t>
+          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5], [665.0, 722.5, 766.0, 749.5]], "answer": "$223.54"}</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5], [781.0, 768.5, 864.0, 795.5]]</t>
+          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5], [665.0, 722.5, 766.0, 749.5]]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -6020,16 +6020,16 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>556598765443260</v>
+        <v>35806346265413</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0001.png</t>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0010.png</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0001.json</t>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0010.json</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6046,1095 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Look at the document in the image: a structured application form with visible section headers and labeled fields. Use the visible section headers and values to answer: In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
+          <t>Use the structured document in the image: a receipt-style document with visible section headers and labeled totals rows. Read the document and answer this question: In the Totals section, what is Items Total plus Tax minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer format: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Use the structured document in the image: a receipt-style document with visible section headers and labeled totals rows. Read the document and answer this question: In the Totals section, what is Items Total plus Tax minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5], [781.0, 768.5, 864.0, 795.5]], "answer": "$49.50"}</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5], [781.0, 768.5, 864.0, 795.5]]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>69880701457133</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0019.png</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0019.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="207.75" customHeight="1">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>sum_minus_amount_in_section</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. Use the visible section headers and values to answer: In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer format: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. Use the visible section headers and values to answer: In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 297.0, 749.5], [665.0, 722.5, 766.0, 749.5]], "answer": "$166.07"}</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 297.0, 749.5], [665.0, 722.5, 766.0, 749.5]]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>179537484972328</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0013.png</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0013.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="207.75" customHeight="1">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>sum_minus_amount_in_section</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: a structured application form with visible section headers and labeled fields. Read the document and answer this question: In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer format: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: a structured application form with visible section headers and labeled fields. Read the document and answer this question: In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 301.0, 791.5]], "answer": "$86.25"}</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>[[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 301.0, 791.5]]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>901607455386425</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0001.png</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0001.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="207.75" customHeight="1">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>sum_minus_amount_in_section</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Read the named sections in this document: a structured application form with visible section headers and labeled fields. Use the visible section headers and values to answer: In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer format: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Read the named sections in this document: a structured application form with visible section headers and labeled fields. Use the visible section headers and values to answer: In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[218.0, 638.5, 337.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 319.0, 791.5]], "answer": "$158.45"}</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>[[218.0, 638.5, 337.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 319.0, 791.5]]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>914946227702172</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0011.png</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0011.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="207.75" customHeight="1">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>sum_minus_amount_in_section</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Read the named sections in this document: a structured application form with visible section headers and labeled fields. Read the document and answer this question: In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Read the named sections in this document: a structured application form with visible section headers and labeled fields. Read the document and answer this question: In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 319.0, 791.5]], "answer": "$109.69"}</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>[[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 319.0, 791.5]]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1047015127982102</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0018.png</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0018.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="207.75" customHeight="1">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>sum_minus_amount_in_section</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. Use the visible section headers and values to answer: In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer format: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. Use the visible section headers and values to answer: In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5], [665.0, 722.5, 766.0, 749.5]], "answer": "$222.05"}</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5], [665.0, 722.5, 766.0, 749.5]]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1110618799388319</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0017.png</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0017.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="207.75" customHeight="1">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>sum_minus_amount_in_section</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. Read the document and answer this question: In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. Read the document and answer this question: In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 297.0, 749.5], [665.0, 722.5, 748.0, 749.5]], "answer": "$289.98"}</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 297.0, 749.5], [665.0, 722.5, 748.0, 749.5]]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1231038124825650</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0014.png</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0014.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="207.75" customHeight="1">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>sum_minus_amount_in_section</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a receipt-style document with visible section headers and labeled totals rows. Use the visible section headers and values to answer: In the Totals section, what is Items Total plus Tax minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a receipt-style document with visible section headers and labeled totals rows. Use the visible section headers and values to answer: In the Totals section, what is Items Total plus Tax minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5], [781.0, 768.5, 864.0, 795.5]], "answer": "$77.18"}</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5], [781.0, 768.5, 864.0, 795.5]]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1581961181402061</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0000.png</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0000.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="207.75" customHeight="1">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>sum_minus_amount_in_section</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>You are given a receipt-style document with visible section headers and labeled totals rows. Use the visible section headers and values to answer: In the Totals section, what is Items Total plus Tax minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>You are given a receipt-style document with visible section headers and labeled totals rows. Use the visible section headers and values to answer: In the Totals section, what is Items Total plus Tax minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5], [781.0, 768.5, 864.0, 795.5]], "answer": "$38.36"}</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5], [781.0, 768.5, 864.0, 795.5]]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>1813189488340421</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0024.png</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0024.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="207.75" customHeight="1">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>sum_minus_amount_in_section</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: a structured application form with visible section headers and labeled fields. Find the named section and then answer: In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: a structured application form with visible section headers and labeled fields. Find the named section and then answer: In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[218.0, 638.5, 337.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 319.0, 791.5]], "answer": "$175.80"}</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>[[218.0, 638.5, 337.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 319.0, 791.5]]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>2467047453400285</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0021.png</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0021.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="207.75" customHeight="1">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>sum_minus_amount_in_section</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Use the structured document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Use the structured document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 297.0, 749.5], [665.0, 722.5, 766.0, 749.5]], "answer": "$287.83"}</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 297.0, 749.5], [665.0, 722.5, 766.0, 749.5]]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>2637489082552279</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0020.png</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0020.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="207.75" customHeight="1">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>sum_minus_amount_in_section</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>You are given a structured application form with visible section headers and labeled fields. Locate the relevant section before computing the answer: In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>You are given a structured application form with visible section headers and labeled fields. Locate the relevant section before computing the answer: In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 319.0, 791.5]], "answer": "$76.72"}</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>[[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 319.0, 791.5]]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>3242494987043318</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0002.png</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0002.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="207.75" customHeight="1">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>sum_minus_amount_in_section</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer format: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5], [665.0, 722.5, 766.0, 749.5]], "answer": "$301.87"}</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5], [665.0, 722.5, 766.0, 749.5]]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>3449753375968602</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0006.png</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0006.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="207.75" customHeight="1">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>sum_minus_amount_in_section</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Read the named sections in this document: an invoice with visible named sections, labeled header fields, and summary blocks. Find the named section and then answer: In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Read the named sections in this document: an invoice with visible named sections, labeled header fields, and summary blocks. Find the named section and then answer: In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 297.0, 749.5], [665.0, 722.5, 766.0, 749.5]], "answer": "$143.52"}</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 297.0, 749.5], [665.0, 722.5, 766.0, 749.5]]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>3710331960120636</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0016.png</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0016.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="207.75" customHeight="1">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>sum_minus_amount_in_section</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>You are given a structured application form with visible section headers and labeled fields. In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer format: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>You are given a structured application form with visible section headers and labeled fields. In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 319.0, 791.5]], "answer": "$130.89"}</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>[[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 319.0, 791.5]]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>4666152458323834</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0003.png</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0003.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="207.75" customHeight="1">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>sum_minus_amount_in_section</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>You are given a structured application form with visible section headers and labeled fields. Locate the relevant section before computing the answer: In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>You are given a structured application form with visible section headers and labeled fields. Locate the relevant section before computing the answer: In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 319.0, 791.5]], "answer": "$102.66"}</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>[[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 319.0, 791.5]]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>5849256945883686</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0012.png</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0012.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="207.75" customHeight="1">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>sum_minus_amount_in_section</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: a structured application form with visible section headers and labeled fields. Locate the relevant section before computing the answer: In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: a structured application form with visible section headers and labeled fields. Locate the relevant section before computing the answer: In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 319.0, 791.5]], "answer": "$87.59"}</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>[[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 319.0, 791.5]]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>5949890584530347</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0005.png</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0005.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="207.75" customHeight="1">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>sum_minus_amount_in_section</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Use the structured document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. Locate the relevant section before computing the answer: In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
 Answer: set "answer" to the computed amount formatted exactly as $0.00.
@@ -6054,63 +7142,191 @@
 {"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Look at the document in the image: a structured application form with visible section headers and labeled fields. Use the visible section headers and values to answer: In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Use the structured document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. Locate the relevant section before computing the answer: In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
 Return a valid JSON object with key "answer".
 Answer: set "answer" to the computed amount formatted exactly as $0.00.
 Example JSON:
 {"answer":"$133.30"}</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 319.0, 791.5]], "answer": "$88.95"}</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>[[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 319.0, 791.5]]</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 297.0, 749.5], [665.0, 722.5, 766.0, 749.5]], "answer": "$228.28"}</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 297.0, 749.5], [665.0, 722.5, 766.0, 749.5]]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>631107804552879</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0011.png</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0011.json</t>
+      <c r="K20" t="n">
+        <v>6368742300615485</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0008.png</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0008.json</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="207.75" customHeight="1">
-      <c r="C4" s="2" t="inlineStr">
+    <row r="21" ht="207.75" customHeight="1">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>task_documents_arithmetic_section_expression_value</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>sum_minus_amount_in_section</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a receipt-style document with visible section headers and labeled totals rows. Find the named section and then answer: In the Totals section, what is Items Total plus Tax minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a structured application form with visible section headers and labeled fields. In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a structured application form with visible section headers and labeled fields. In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[218.0, 638.5, 337.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 319.0, 791.5]], "answer": "$168.33"}</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>[[218.0, 638.5, 337.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 319.0, 791.5]]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>6534975518876904</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0023.png</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0023.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="207.75" customHeight="1">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>sum_minus_amount_in_section</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>You are given an invoice with visible named sections, labeled header fields, and summary blocks. Locate the relevant section before computing the answer: In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>You are given an invoice with visible named sections, labeled header fields, and summary blocks. Locate the relevant section before computing the answer: In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$133.30"}</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 297.0, 749.5], [665.0, 722.5, 766.0, 749.5]], "answer": "$193.16"}</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 297.0, 749.5], [665.0, 722.5, 766.0, 749.5]]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>6586591020932590</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0022.png</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0022.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="207.75" customHeight="1">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>sum_minus_amount_in_section</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. Find the named section and then answer: In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
 Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
@@ -6118,63 +7334,63 @@
 {"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a receipt-style document with visible section headers and labeled totals rows. Find the named section and then answer: In the Totals section, what is Items Total plus Tax minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. Find the named section and then answer: In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
 Return a valid JSON object with key "answer".
 Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
 Example JSON:
 {"answer":"$133.30"}</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5], [781.0, 768.5, 864.0, 795.5]], "answer": "$64.39"}</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5], [781.0, 768.5, 864.0, 795.5]]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5], [665.0, 722.5, 766.0, 749.5]], "answer": "$143.96"}</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5], [665.0, 722.5, 766.0, 749.5]]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>857607781687074</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0022.png</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0022.json</t>
+      <c r="K23" t="n">
+        <v>7223335851502769</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0015.png</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0015.json</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="207.75" customHeight="1">
-      <c r="C5" s="2" t="inlineStr">
+    <row r="24" ht="207.75" customHeight="1">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>task_documents_arithmetic_section_expression_value</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>sum_minus_amount_in_section</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Look at the document in the image: a structured application form with visible section headers and labeled fields. Locate the relevant section before computing the answer: In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>You are given an invoice with visible named sections, labeled header fields, and summary blocks. Find the named section and then answer: In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
 Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
@@ -6182,255 +7398,63 @@
 {"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Look at the document in the image: a structured application form with visible section headers and labeled fields. Locate the relevant section before computing the answer: In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>You are given an invoice with visible named sections, labeled header fields, and summary blocks. Find the named section and then answer: In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
 Return a valid JSON object with key "answer".
-Answer format: set "answer" to the computed amount formatted exactly as $0.00.
+Answer: set "answer" to the computed amount formatted exactly as $0.00.
 Example JSON:
 {"answer":"$133.30"}</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 319.0, 791.5]], "answer": "$62.66"}</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>[[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 319.0, 791.5]]</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5], [665.0, 722.5, 766.0, 749.5]], "answer": "$288.53"}</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5], [665.0, 722.5, 766.0, 749.5]]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>1049391872335901</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0003.png</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0003.json</t>
+      <c r="K24" t="n">
+        <v>7286838615254028</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0007.png</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0007.json</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="207.75" customHeight="1">
-      <c r="C6" s="2" t="inlineStr">
+    <row r="25" ht="207.75" customHeight="1">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>task_documents_arithmetic_section_expression_value</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>sum_minus_amount_in_section</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Look at the document in the image: a receipt-style document with visible section headers and labeled totals rows. Use the visible section headers and values to answer: In the Totals section, what is Items Total plus Tax minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer field: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Look at the document in the image: a receipt-style document with visible section headers and labeled totals rows. Use the visible section headers and values to answer: In the Totals section, what is Items Total plus Tax minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5], [781.0, 768.5, 864.0, 795.5]], "answer": "$70.00"}</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5], [781.0, 768.5, 864.0, 795.5]]</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>1266489807378371</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0014.png</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0014.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="207.75" customHeight="1">
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>sum_minus_amount_in_section</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Use the structured document in the image: a structured application form with visible section headers and labeled fields. Read the document and answer this question: In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Use the structured document in the image: a structured application form with visible section headers and labeled fields. Read the document and answer this question: In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 319.0, 791.5]], "answer": "$110.37"}</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>[[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 319.0, 791.5]]</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>1599346056699310</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0005.png</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0005.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="207.75" customHeight="1">
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>sum_minus_amount_in_section</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Use the structured document in the image: a receipt-style document with visible section headers and labeled totals rows. In the Totals section, what is Items Total plus Tax minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Use the structured document in the image: a receipt-style document with visible section headers and labeled totals rows. In the Totals section, what is Items Total plus Tax minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5], [781.0, 768.5, 864.0, 795.5]], "answer": "$56.69"}</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5], [781.0, 768.5, 864.0, 795.5]]</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>2163572550461201</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0009.png</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0009.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="207.75" customHeight="1">
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>sum_minus_amount_in_section</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a receipt-style document with visible section headers and labeled totals rows. Find the named section and then answer: In the Totals section, what is Items Total plus Tax minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>The image shows an invoice with visible named sections, labeled header fields, and summary blocks. Locate the relevant section before computing the answer: In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
 Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
@@ -6438,511 +7462,63 @@
 {"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a receipt-style document with visible section headers and labeled totals rows. Find the named section and then answer: In the Totals section, what is Items Total plus Tax minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5], [781.0, 768.5, 864.0, 795.5]], "answer": "$54.67"}</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5], [781.0, 768.5, 864.0, 795.5]]</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>2338969079340574</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0007.png</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0007.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="207.75" customHeight="1">
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>sum_minus_amount_in_section</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>You are given a structured application form with visible section headers and labeled fields. Use the visible section headers and values to answer: In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer field: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>You are given a structured application form with visible section headers and labeled fields. Use the visible section headers and values to answer: In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>The image shows an invoice with visible named sections, labeled header fields, and summary blocks. Locate the relevant section before computing the answer: In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
 Return a valid JSON object with key "answer".
 Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
 Example JSON:
 {"answer":"$133.30"}</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 301.0, 791.5]], "answer": "$131.97"}</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>[[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 301.0, 791.5]]</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 297.0, 749.5], [665.0, 722.5, 748.0, 749.5]], "answer": "$324.35"}</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 297.0, 749.5], [665.0, 722.5, 748.0, 749.5]]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K10" t="n">
-        <v>2363404767288889</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0018.png</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0018.json</t>
+      <c r="K25" t="n">
+        <v>8135010964262470</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0009.png</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0009.json</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="207.75" customHeight="1">
-      <c r="C11" s="2" t="inlineStr">
+    <row r="26" ht="207.75" customHeight="1">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>task_documents_arithmetic_section_expression_value</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>sum_minus_amount_in_section</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Use the structured document in the image: a receipt-style document with visible section headers and labeled totals rows. In the Totals section, what is Items Total plus Tax minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Use the structured document in the image: a receipt-style document with visible section headers and labeled totals rows. In the Totals section, what is Items Total plus Tax minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5], [781.0, 768.5, 864.0, 795.5]], "answer": "$74.15"}</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5], [781.0, 768.5, 864.0, 795.5]]</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>3048798153929734</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0006.png</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0006.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="207.75" customHeight="1">
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>sum_minus_amount_in_section</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Use the structured document in the image: a receipt-style document with visible section headers and labeled totals rows. Use the visible section headers and values to answer: In the Totals section, what is Items Total plus Tax minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer format: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Use the structured document in the image: a receipt-style document with visible section headers and labeled totals rows. Use the visible section headers and values to answer: In the Totals section, what is Items Total plus Tax minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5], [781.0, 768.5, 864.0, 795.5]], "answer": "$63.12"}</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5], [781.0, 768.5, 864.0, 795.5]]</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>3318068441621607</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0020.png</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0020.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="207.75" customHeight="1">
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>sum_minus_amount_in_section</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: an invoice with visible named sections, labeled header fields, and summary blocks. In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: an invoice with visible named sections, labeled header fields, and summary blocks. In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5], [665.0, 722.5, 748.0, 749.5]], "answer": "$188.01"}</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5], [665.0, 722.5, 748.0, 749.5]]</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>3844100963770675</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0021.png</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0021.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="207.75" customHeight="1">
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>sum_minus_amount_in_section</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: an invoice with visible named sections, labeled header fields, and summary blocks. Use the visible section headers and values to answer: In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: an invoice with visible named sections, labeled header fields, and summary blocks. Use the visible section headers and values to answer: In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 297.0, 749.5], [665.0, 722.5, 766.0, 749.5]], "answer": "$142.01"}</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 297.0, 749.5], [665.0, 722.5, 766.0, 749.5]]</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>4093072637577253</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0019.png</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0019.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="207.75" customHeight="1">
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>sum_minus_amount_in_section</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a receipt-style document with visible section headers and labeled totals rows. Find the named section and then answer: In the Totals section, what is Items Total plus Tax minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer field: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a receipt-style document with visible section headers and labeled totals rows. Find the named section and then answer: In the Totals section, what is Items Total plus Tax minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5], [781.0, 768.5, 864.0, 795.5]], "answer": "$86.97"}</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5], [781.0, 768.5, 864.0, 795.5]]</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>4173056392035471</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0002.png</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0002.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="207.75" customHeight="1">
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>sum_minus_amount_in_section</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: an invoice with visible named sections, labeled header fields, and summary blocks. Read the document and answer this question: In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer field: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: an invoice with visible named sections, labeled header fields, and summary blocks. Read the document and answer this question: In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5], [665.0, 722.5, 766.0, 749.5]], "answer": "$331.65"}</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5], [665.0, 722.5, 766.0, 749.5]]</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>4198431566823653</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0004.png</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0004.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="207.75" customHeight="1">
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>sum_minus_amount_in_section</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: a receipt-style document with visible section headers and labeled totals rows. Locate the relevant section before computing the answer: In the Totals section, what is Items Total plus Tax minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: a receipt-style document with visible section headers and labeled totals rows. Read the document and answer this question: In the Totals section, what is Items Total plus Tax minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
 Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
@@ -6950,622 +7526,46 @@
 {"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: a receipt-style document with visible section headers and labeled totals rows. Locate the relevant section before computing the answer: In the Totals section, what is Items Total plus Tax minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5], [781.0, 768.5, 864.0, 795.5]], "answer": "$56.58"}</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5], [781.0, 768.5, 864.0, 795.5]]</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>4882817036351389</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0023.png</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0023.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="207.75" customHeight="1">
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>sum_minus_amount_in_section</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>You are given a structured application form with visible section headers and labeled fields. Read the document and answer this question: In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>You are given a structured application form with visible section headers and labeled fields. Read the document and answer this question: In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[218.0, 638.5, 337.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 319.0, 791.5]], "answer": "$186.89"}</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>[[218.0, 638.5, 337.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 319.0, 791.5]]</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>4961384568716670</v>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0000.png</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0000.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="207.75" customHeight="1">
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>sum_minus_amount_in_section</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: a receipt-style document with visible section headers and labeled totals rows. Find the named section and then answer: In the Totals section, what is Items Total plus Tax minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: a receipt-style document with visible section headers and labeled totals rows. Find the named section and then answer: In the Totals section, what is Items Total plus Tax minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5], [781.0, 768.5, 864.0, 795.5]], "answer": "$98.28"}</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5], [781.0, 768.5, 864.0, 795.5]]</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>4962565511975784</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0013.png</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0013.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="207.75" customHeight="1">
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>sum_minus_amount_in_section</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: a receipt-style document with visible section headers and labeled totals rows. Use the visible section headers and values to answer: In the Totals section, what is Items Total plus Tax minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: a receipt-style document with visible section headers and labeled totals rows. Use the visible section headers and values to answer: In the Totals section, what is Items Total plus Tax minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5], [781.0, 768.5, 864.0, 795.5]], "answer": "$40.26"}</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5], [781.0, 768.5, 864.0, 795.5]]</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>5538413780907069</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0015.png</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0015.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="207.75" customHeight="1">
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>sum_minus_amount_in_section</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Use the structured document in the image: a structured application form with visible section headers and labeled fields. Use the visible section headers and values to answer: In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Use the structured document in the image: a structured application form with visible section headers and labeled fields. Use the visible section headers and values to answer: In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Compute the exact amount from the shown values.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[218.0, 638.5, 337.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 319.0, 791.5]], "answer": "$187.62"}</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>[[218.0, 638.5, 337.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 319.0, 791.5]]</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>6239527200301001</v>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0010.png</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0010.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="207.75" customHeight="1">
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>sum_minus_amount_in_section</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Look at the document in the image: a structured application form with visible section headers and labeled fields. Use the visible section headers and values to answer: In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer format: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Look at the document in the image: a structured application form with visible section headers and labeled fields. Use the visible section headers and values to answer: In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 301.0, 791.5]], "answer": "$127.30"}</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>[[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 301.0, 791.5]]</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>6527620112336411</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0016.png</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0016.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="207.75" customHeight="1">
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>sum_minus_amount_in_section</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>The image shows an invoice with visible named sections, labeled header fields, and summary blocks. In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>The image shows an invoice with visible named sections, labeled header fields, and summary blocks. In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5], [665.0, 722.5, 766.0, 749.5]], "answer": "$326.72"}</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5], [665.0, 722.5, 766.0, 749.5]]</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>6536789372924166</v>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0012.png</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0012.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="207.75" customHeight="1">
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>sum_minus_amount_in_section</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Use the structured document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. Read the document and answer this question: In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer format: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Use the structured document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. Read the document and answer this question: In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Return the computed amount in the same currency format.
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: a receipt-style document with visible section headers and labeled totals rows. Read the document and answer this question: In the Totals section, what is Items Total plus Tax minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
 Return a valid JSON object with key "answer".
 Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
 Example JSON:
 {"answer":"$133.30"}</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5], [665.0, 722.5, 748.0, 749.5]], "answer": "$278.60"}</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5], [665.0, 722.5, 748.0, 749.5]]</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5], [781.0, 768.5, 864.0, 795.5]], "answer": "$44.12"}</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5], [781.0, 768.5, 864.0, 795.5]]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K24" t="n">
-        <v>6566124760246976</v>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0024.png</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0024.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="207.75" customHeight="1">
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>sum_minus_amount_in_section</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Use the structured document in the image: a structured application form with visible section headers and labeled fields. Locate the relevant section before computing the answer: In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer field: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Use the structured document in the image: a structured application form with visible section headers and labeled fields. Locate the relevant section before computing the answer: In the Fees section, what is Registration Fee plus Service Fee minus Discount? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 301.0, 791.5]], "answer": "$110.56"}</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>[[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5], [218.0, 764.5, 301.0, 791.5]]</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>6693679739184451</v>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0008.png</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0008.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="207.75" customHeight="1">
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>sum_minus_amount_in_section</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Use the structured document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354],[150,380,364,414]],"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Use the structured document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. In the Billing Summary section, what is Subtotal plus Tax minus Discount? Return the amount as $0.00. Answer using the resulting amount only.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$133.30"}</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5], [665.0, 722.5, 766.0, 749.5]], "answer": "$331.93"}</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5], [665.0, 722.5, 766.0, 749.5]]</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
       <c r="K26" t="n">
-        <v>8399982947143217</v>
+        <v>8478575442161091</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0017.png</t>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_minus_amount_in_section/0004.png</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0017.json</t>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_minus_amount_in_section/0004.json</t>
         </is>
       </c>
     </row>
@@ -7679,17 +7679,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>You are given a structured application form with visible section headers and labeled fields. Read the document and answer this question: In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Return the computed amount in the same currency format.
+          <t>You are given an invoice with visible named sections, labeled header fields, and summary blocks. In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
+Evidence: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer: set "answer" to the computed amount formatted exactly as $0.00.
 Example JSON:
 {"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>You are given a structured application form with visible section headers and labeled fields. Read the document and answer this question: In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Return the computed amount in the same currency format.
+          <t>You are given an invoice with visible named sections, labeled header fields, and summary blocks. In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
 Return a valid JSON object with key "answer".
 Answer format: set "answer" to the computed amount formatted exactly as $0.00.
 Example JSON:
@@ -7698,12 +7698,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": [[218.0, 638.5, 337.0, 665.5], [666.0, 638.5, 767.0, 665.5]], "answer": "$212.44"}</t>
+          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5]], "answer": "$153.39"}</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>[[218.0, 638.5, 337.0, 665.5], [666.0, 638.5, 767.0, 665.5]]</t>
+          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5]]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -7717,16 +7717,16 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>224934501252867</v>
+        <v>657293776614265</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0001.png</t>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0006.png</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0001.json</t>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0006.json</t>
         </is>
       </c>
     </row>
@@ -7743,31 +7743,31 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Look at the document in the image: a structured application form with visible section headers and labeled fields. Find the named section and then answer: In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Return the computed amount in the same currency format.
+          <t>You are given a receipt-style document with visible section headers and labeled totals rows. In the Totals section, what is Items Total plus Tax? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
+Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
 Example JSON:
 {"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Look at the document in the image: a structured application form with visible section headers and labeled fields. Find the named section and then answer: In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Return the computed amount in the same currency format.
+          <t>You are given a receipt-style document with visible section headers and labeled totals rows. In the Totals section, what is Items Total plus Tax? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
 Return a valid JSON object with key "answer".
-Answer format: set "answer" to the computed amount formatted exactly as $0.00.
+Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
 Example JSON:
 {"answer":"$146.80"}</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": [[218.0, 638.5, 337.0, 665.5], [666.0, 638.5, 767.0, 665.5]], "answer": "$196.68"}</t>
+          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5]], "answer": "$92.46"}</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>[[218.0, 638.5, 337.0, 665.5], [666.0, 638.5, 767.0, 665.5]]</t>
+          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5]]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -7781,16 +7781,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>290332693162733</v>
+        <v>784325438053578</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0018.png</t>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0001.png</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0018.json</t>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0001.json</t>
         </is>
       </c>
     </row>
@@ -7806,1414 +7806,6 @@
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>You are given a structured application form with visible section headers and labeled fields. Find the named section and then answer: In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Compute the exact amount from the shown values.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>You are given a structured application form with visible section headers and labeled fields. Find the named section and then answer: In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Compute the exact amount from the shown values.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[218.0, 638.5, 337.0, 665.5], [666.0, 638.5, 767.0, 665.5]], "answer": "$165.43"}</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>[[218.0, 638.5, 337.0, 665.5], [666.0, 638.5, 767.0, 665.5]]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>825052951155962</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0024.png</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0024.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="207.75" customHeight="1">
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>sum_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Use the structured document in the image: a structured application form with visible section headers and labeled fields. Locate the relevant section before computing the answer: In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Answer using the resulting amount only.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Use the structured document in the image: a structured application form with visible section headers and labeled fields. Locate the relevant section before computing the answer: In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Answer using the resulting amount only.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[218.0, 638.5, 337.0, 665.5], [666.0, 638.5, 767.0, 665.5]], "answer": "$178.13"}</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>[[218.0, 638.5, 337.0, 665.5], [666.0, 638.5, 767.0, 665.5]]</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>2098588899322867</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0005.png</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0005.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="207.75" customHeight="1">
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>sum_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: an invoice with visible named sections, labeled header fields, and summary blocks. Find the named section and then answer: In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Answer using the resulting amount only.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: an invoice with visible named sections, labeled header fields, and summary blocks. Find the named section and then answer: In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Answer using the resulting amount only.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5]], "answer": "$347.47"}</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5]]</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>2213399193055323</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0020.png</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0020.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="207.75" customHeight="1">
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>sum_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: an invoice with visible named sections, labeled header fields, and summary blocks. Use the visible section headers and values to answer: In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Compute the exact amount from the shown values.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer format: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: an invoice with visible named sections, labeled header fields, and summary blocks. Use the visible section headers and values to answer: In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Compute the exact amount from the shown values.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 297.0, 749.5]], "answer": "$190.87"}</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 297.0, 749.5]]</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>2272087831179991</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0010.png</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0010.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="207.75" customHeight="1">
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>sum_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Look at the document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. Find the named section and then answer: In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Answer using the resulting amount only.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer field: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Look at the document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. Find the named section and then answer: In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Answer using the resulting amount only.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 297.0, 749.5]], "answer": "$300.10"}</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 297.0, 749.5]]</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>3507062736953068</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0007.png</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0007.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="207.75" customHeight="1">
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>sum_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Look at the document in the image: a receipt-style document with visible section headers and labeled totals rows. Find the named section and then answer: In the Totals section, what is Items Total plus Tax? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer field: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Look at the document in the image: a receipt-style document with visible section headers and labeled totals rows. Find the named section and then answer: In the Totals section, what is Items Total plus Tax? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5]], "answer": "$62.17"}</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5]]</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>3839588646525744</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0011.png</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0011.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="207.75" customHeight="1">
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>sum_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>You are given a structured application form with visible section headers and labeled fields. In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Compute the exact amount from the shown values.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>You are given a structured application form with visible section headers and labeled fields. In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Compute the exact amount from the shown values.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5]], "answer": "$139.87"}</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>[[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5]]</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>4247568772245571</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0019.png</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0019.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="207.75" customHeight="1">
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>sum_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: a receipt-style document with visible section headers and labeled totals rows. In the Totals section, what is Items Total plus Tax? Return the amount as $0.00. Compute the exact amount from the shown values.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: a receipt-style document with visible section headers and labeled totals rows. In the Totals section, what is Items Total plus Tax? Return the amount as $0.00. Compute the exact amount from the shown values.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5]], "answer": "$63.82"}</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5]]</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>4497388373859302</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0021.png</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0021.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="207.75" customHeight="1">
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>sum_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Look at the document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Answer using the resulting amount only.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer format: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Look at the document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Answer using the resulting amount only.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5]], "answer": "$142.62"}</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5]]</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>4769506942451024</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0009.png</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0009.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="207.75" customHeight="1">
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>sum_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Look at the document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Answer using the resulting amount only.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Look at the document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Answer using the resulting amount only.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5]], "answer": "$270.40"}</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5]]</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>5033038138026786</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0016.png</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0016.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="207.75" customHeight="1">
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>sum_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Look at the document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. Use the visible section headers and values to answer: In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Answer using the resulting amount only.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer format: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Look at the document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. Use the visible section headers and values to answer: In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Answer using the resulting amount only.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 297.0, 749.5]], "answer": "$209.88"}</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 297.0, 749.5]]</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>5908232218472490</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0003.png</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0003.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="207.75" customHeight="1">
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>sum_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>You are given a receipt-style document with visible section headers and labeled totals rows. Read the document and answer this question: In the Totals section, what is Items Total plus Tax? Return the amount as $0.00. Answer using the resulting amount only.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>You are given a receipt-style document with visible section headers and labeled totals rows. Read the document and answer this question: In the Totals section, what is Items Total plus Tax? Return the amount as $0.00. Answer using the resulting amount only.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5]], "answer": "$69.38"}</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5]]</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>6078710524110572</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0000.png</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0000.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="207.75" customHeight="1">
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>sum_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: a structured application form with visible section headers and labeled fields. Find the named section and then answer: In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Return the computed amount in the same currency format.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: a structured application form with visible section headers and labeled fields. Find the named section and then answer: In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Return the computed amount in the same currency format.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[218.0, 638.5, 337.0, 665.5], [666.0, 638.5, 767.0, 665.5]], "answer": "$144.70"}</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>[[218.0, 638.5, 337.0, 665.5], [666.0, 638.5, 767.0, 665.5]]</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>6142455986090545</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0017.png</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0017.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="207.75" customHeight="1">
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>sum_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a receipt-style document with visible section headers and labeled totals rows. Read the document and answer this question: In the Totals section, what is Items Total plus Tax? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a receipt-style document with visible section headers and labeled totals rows. Read the document and answer this question: In the Totals section, what is Items Total plus Tax? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5]], "answer": "$99.30"}</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5]]</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>6167768339298348</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0012.png</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0012.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="207.75" customHeight="1">
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>sum_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>You are given an invoice with visible named sections, labeled header fields, and summary blocks. Use the visible section headers and values to answer: In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Compute the exact amount from the shown values.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer format: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>You are given an invoice with visible named sections, labeled header fields, and summary blocks. Use the visible section headers and values to answer: In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Compute the exact amount from the shown values.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5]], "answer": "$207.91"}</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5]]</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>6485929574077864</v>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0006.png</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0006.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="207.75" customHeight="1">
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>sum_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: a structured application form with visible section headers and labeled fields. Locate the relevant section before computing the answer: In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer format: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: a structured application form with visible section headers and labeled fields. Locate the relevant section before computing the answer: In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5]], "answer": "$125.46"}</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>[[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5]]</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>6641985790866478</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0014.png</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0014.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="207.75" customHeight="1">
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>sum_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: a receipt-style document with visible section headers and labeled totals rows. In the Totals section, what is Items Total plus Tax? Return the amount as $0.00. Return the computed amount in the same currency format.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer field: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: a receipt-style document with visible section headers and labeled totals rows. In the Totals section, what is Items Total plus Tax? Return the amount as $0.00. Return the computed amount in the same currency format.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5]], "answer": "$102.14"}</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5]]</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>7104478733731302</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0023.png</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0023.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="207.75" customHeight="1">
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>sum_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: a structured application form with visible section headers and labeled fields. In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Return the computed amount in the same currency format.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Read the named sections in this document: a structured application form with visible section headers and labeled fields. In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Return the computed amount in the same currency format.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5]], "answer": "$136.13"}</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>[[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5]]</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>7292162401122514</v>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0015.png</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0015.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="207.75" customHeight="1">
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>sum_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>You are given a receipt-style document with visible section headers and labeled totals rows. Use the visible section headers and values to answer: In the Totals section, what is Items Total plus Tax? Return the amount as $0.00. Compute the exact amount from the shown values.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>You are given a receipt-style document with visible section headers and labeled totals rows. Use the visible section headers and values to answer: In the Totals section, what is Items Total plus Tax? Return the amount as $0.00. Compute the exact amount from the shown values.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5]], "answer": "$86.84"}</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5]]</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>7544721384449000</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0008.png</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0008.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="207.75" customHeight="1">
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>sum_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Use the structured document in the image: a structured application form with visible section headers and labeled fields. Use the visible section headers and values to answer: In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Return the computed amount in the same currency format.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Use the structured document in the image: a structured application form with visible section headers and labeled fields. Use the visible section headers and values to answer: In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Return the computed amount in the same currency format.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5]], "answer": "$92.23"}</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>[[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5]]</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>8014433313462334</v>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0004.png</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0004.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="207.75" customHeight="1">
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>sum_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Use the structured document in the image: a receipt-style document with visible section headers and labeled totals rows. Read the document and answer this question: In the Totals section, what is Items Total plus Tax? Return the amount as $0.00. Answer using the resulting amount only.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Use the structured document in the image: a receipt-style document with visible section headers and labeled totals rows. Read the document and answer this question: In the Totals section, what is Items Total plus Tax? Return the amount as $0.00. Answer using the resulting amount only.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5]], "answer": "$58.23"}</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5]]</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>8049917561991165</v>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0013.png</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0013.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="207.75" customHeight="1">
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>sum_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Look at the document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. Read the document and answer this question: In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Compute the exact amount from the shown values.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
-Answer format: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Look at the document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. Read the document and answer this question: In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Compute the exact amount from the shown values.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the computed amount formatted exactly as $0.00.
-Example JSON:
-{"answer":"$146.80"}</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5]], "answer": "$353.21"}</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5]]</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>8309395279834385</v>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0002.png</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0002.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="207.75" customHeight="1">
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>task_documents_arithmetic_section_expression_value</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>sum_two_amounts_in_section</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Look at the document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. Find the named section and then answer: In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Compute the exact amount from the shown values.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
@@ -9223,23 +7815,1431 @@
 {"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Look at the document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. Find the named section and then answer: In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Compute the exact amount from the shown values.
 Return a valid JSON object with key "answer".
+Answer: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 297.0, 749.5]], "answer": "$251.71"}</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 297.0, 749.5]]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>811012893470000</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0020.png</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0020.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="207.75" customHeight="1">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>sum_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Use the structured document in the image: a receipt-style document with visible section headers and labeled totals rows. Read the document and answer this question: In the Totals section, what is Items Total plus Tax? Return the amount as $0.00. Compute the exact amount from the shown values.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Use the structured document in the image: a receipt-style document with visible section headers and labeled totals rows. Read the document and answer this question: In the Totals section, what is Items Total plus Tax? Return the amount as $0.00. Compute the exact amount from the shown values.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5]], "answer": "$98.31"}</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5]]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>976629808865746</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0008.png</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0008.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="207.75" customHeight="1">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>sum_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>You are given an invoice with visible named sections, labeled header fields, and summary blocks. Read the document and answer this question: In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>You are given an invoice with visible named sections, labeled header fields, and summary blocks. Read the document and answer this question: In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5]], "answer": "$271.73"}</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5]]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1007061304667234</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0018.png</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0018.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="207.75" customHeight="1">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>sum_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>The image shows an invoice with visible named sections, labeled header fields, and summary blocks. Use the visible section headers and values to answer: In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>The image shows an invoice with visible named sections, labeled header fields, and summary blocks. Use the visible section headers and values to answer: In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5]], "answer": "$294.10"}</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5]]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1726365213973749</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0011.png</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0011.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="207.75" customHeight="1">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>sum_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>You are given an invoice with visible named sections, labeled header fields, and summary blocks. Locate the relevant section before computing the answer: In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Return the computed amount in the same currency format.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>You are given an invoice with visible named sections, labeled header fields, and summary blocks. Locate the relevant section before computing the answer: In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Return the computed amount in the same currency format.
+Return a valid JSON object with key "answer".
 Answer format: set "answer" to the computed amount formatted exactly as $0.00.
 Example JSON:
 {"answer":"$146.80"}</t>
         </is>
       </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5]], "answer": "$312.16"}</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5]]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>2356683938867420</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0010.png</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0010.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="207.75" customHeight="1">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>sum_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Read the named sections in this document: a structured application form with visible section headers and labeled fields. In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Read the named sections in this document: a structured application form with visible section headers and labeled fields. In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5]], "answer": "$83.06"}</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>[[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5]]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>2449586489673410</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0007.png</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0007.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="207.75" customHeight="1">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>sum_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Read the named sections in this document: a structured application form with visible section headers and labeled fields. Use the visible section headers and values to answer: In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Answer using the resulting amount only.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Read the named sections in this document: a structured application form with visible section headers and labeled fields. Use the visible section headers and values to answer: In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Answer using the resulting amount only.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5]], "answer": "$108.99"}</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>[[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5]]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>2708126207987451</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0017.png</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0017.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="207.75" customHeight="1">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>sum_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>The image shows an invoice with visible named sections, labeled header fields, and summary blocks. Use the visible section headers and values to answer: In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Answer using the resulting amount only.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>The image shows an invoice with visible named sections, labeled header fields, and summary blocks. Use the visible section headers and values to answer: In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Answer using the resulting amount only.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5]], "answer": "$199.61"}</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5]]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>3671124063184594</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0009.png</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0009.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="207.75" customHeight="1">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>sum_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>You are given a structured application form with visible section headers and labeled fields. In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>You are given a structured application form with visible section headers and labeled fields. In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[218.0, 638.5, 337.0, 665.5], [666.0, 638.5, 767.0, 665.5]], "answer": "$168.55"}</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>[[218.0, 638.5, 337.0, 665.5], [666.0, 638.5, 767.0, 665.5]]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>3963410821505448</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0004.png</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0004.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="207.75" customHeight="1">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>sum_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: a structured application form with visible section headers and labeled fields. Find the named section and then answer: In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: a structured application form with visible section headers and labeled fields. Find the named section and then answer: In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5]], "answer": "$126.88"}</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>[[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5]]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>4260239657474244</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0000.png</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0000.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="207.75" customHeight="1">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>sum_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Use the structured document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Return the computed amount in the same currency format.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Use the structured document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Return the computed amount in the same currency format.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5]], "answer": "$262.87"}</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5]]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>4400547278857443</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0019.png</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0019.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="207.75" customHeight="1">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>sum_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Use the structured document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. Locate the relevant section before computing the answer: In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Compute the exact amount from the shown values.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Use the structured document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. Locate the relevant section before computing the answer: In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Compute the exact amount from the shown values.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 297.0, 749.5]], "answer": "$315.16"}</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 297.0, 749.5]]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>4792397685250813</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0016.png</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0016.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="207.75" customHeight="1">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>sum_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>The image shows an invoice with visible named sections, labeled header fields, and summary blocks. In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Compute the exact amount from the shown values.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>The image shows an invoice with visible named sections, labeled header fields, and summary blocks. In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Compute the exact amount from the shown values.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5]], "answer": "$260.79"}</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5]]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>5074042373852904</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0014.png</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0014.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="207.75" customHeight="1">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>sum_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: a structured application form with visible section headers and labeled fields. Read the document and answer this question: In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Answer using the resulting amount only.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: a structured application form with visible section headers and labeled fields. Read the document and answer this question: In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Answer using the resulting amount only.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5]], "answer": "$137.67"}</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>[[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5]]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>5100377542884739</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0003.png</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0003.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="207.75" customHeight="1">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>sum_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a structured application form with visible section headers and labeled fields. Read the document and answer this question: In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Return the computed amount in the same currency format.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a structured application form with visible section headers and labeled fields. Read the document and answer this question: In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Return the computed amount in the same currency format.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[218.0, 638.5, 337.0, 665.5], [666.0, 638.5, 767.0, 665.5]], "answer": "$200.17"}</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>[[218.0, 638.5, 337.0, 665.5], [666.0, 638.5, 767.0, 665.5]]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>5189383211116638</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0013.png</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0013.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="207.75" customHeight="1">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>sum_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. Use the visible section headers and values to answer: In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Return the computed amount in the same currency format.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Look at the document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. Use the visible section headers and values to answer: In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Return the computed amount in the same currency format.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 297.0, 749.5]], "answer": "$181.32"}</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 297.0, 749.5]]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>5345941188305883</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0024.png</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0024.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="207.75" customHeight="1">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>sum_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a structured application form with visible section headers and labeled fields. Find the named section and then answer: In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Answer using the resulting amount only.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a structured application form with visible section headers and labeled fields. Find the named section and then answer: In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Answer using the resulting amount only.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[218.0, 638.5, 337.0, 665.5], [666.0, 638.5, 767.0, 665.5]], "answer": "$181.36"}</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>[[218.0, 638.5, 337.0, 665.5], [666.0, 638.5, 767.0, 665.5]]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>5594565850134273</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0005.png</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0005.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="207.75" customHeight="1">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>sum_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>The image shows an invoice with visible named sections, labeled header fields, and summary blocks. Read the document and answer this question: In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer format: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>The image shows an invoice with visible named sections, labeled header fields, and summary blocks. Read the document and answer this question: In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 297.0, 749.5]], "answer": "$248.59"}</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 297.0, 749.5]]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>5843148374668083</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0022.png</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0022.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="207.75" customHeight="1">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>sum_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Use the structured document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Use the structured document in the image: an invoice with visible named sections, labeled header fields, and summary blocks. In the Billing Summary section, what is Subtotal plus Tax? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5]], "answer": "$211.67"}</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5]]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>6264637561008563</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0023.png</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0023.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="207.75" customHeight="1">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>sum_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Use the structured document in the image: a receipt-style document with visible section headers and labeled totals rows. Read the document and answer this question: In the Totals section, what is Items Total plus Tax? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer format: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Use the structured document in the image: a receipt-style document with visible section headers and labeled totals rows. Read the document and answer this question: In the Totals section, what is Items Total plus Tax? Return the amount as $0.00. Respond with the exact amount obtained from the visible values.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5]], "answer": "$45.50"}</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>[[763.0, 628.5, 864.0, 655.5], [781.0, 698.5, 864.0, 725.5]]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>7494768934353406</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0015.png</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0015.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="207.75" customHeight="1">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>sum_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a structured application form with visible section headers and labeled fields. Read the document and answer this question: In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Answer using the resulting amount only.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a structured application form with visible section headers and labeled fields. Read the document and answer this question: In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Answer using the resulting amount only.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[218.0, 638.5, 337.0, 665.5], [666.0, 638.5, 767.0, 665.5]], "answer": "$171.41"}</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>[[218.0, 638.5, 337.0, 665.5], [666.0, 638.5, 767.0, 665.5]]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>7856139154263107</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0021.png</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0021.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="207.75" customHeight="1">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>sum_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a structured application form with visible section headers and labeled fields. In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Compute the exact amount from the shown values.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer requirement: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a structured application form with visible section headers and labeled fields. In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Compute the exact amount from the shown values.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5]], "answer": "$113.69"}</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>[[218.0, 638.5, 319.0, 665.5], [666.0, 638.5, 767.0, 665.5]]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>7973739340229329</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0002.png</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0002.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="207.75" customHeight="1">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>task_documents_arithmetic_section_expression_value</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>sum_two_amounts_in_section</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a structured application form with visible section headers and labeled fields. Find the named section and then answer: In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing one bounding box for each referenced operand value, in the same order as the expression in the prompt.
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"evidence":[[150,260,364,294],[150,320,364,354]],"answer":"$146.80"}</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a structured application form with visible section headers and labeled fields. Find the named section and then answer: In the Fees section, what is Registration Fee plus Service Fee? Return the amount as $0.00. Give the computed amount as written in $0.00 format.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the computed amount formatted exactly as $0.00.
+Example JSON:
+{"answer":"$146.80"}</t>
+        </is>
+      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": [[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5]], "answer": "$294.51"}</t>
+          <t>{"evidence": [[218.0, 638.5, 337.0, 665.5], [666.0, 638.5, 767.0, 665.5]], "answer": "$212.56"}</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>[[665.0, 601.5, 784.0, 628.5], [214.0, 722.5, 315.0, 749.5]]</t>
+          <t>[[218.0, 638.5, 337.0, 665.5], [666.0, 638.5, 767.0, 665.5]]</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -9253,16 +9253,16 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>8893088834209046</v>
+        <v>8920633396638144</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0022.png</t>
+          <t>documents/task_documents_arithmetic_section_expression_value/images/sum_two_amounts_in_section/0012.png</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0022.json</t>
+          <t>documents/task_documents_arithmetic_section_expression_value/data/sum_two_amounts_in_section/0012.json</t>
         </is>
       </c>
     </row>
